--- a/unit_mix_adj_example.xlsx
+++ b/unit_mix_adj_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyson.king\Documents\testing_work\comps_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59DB3BF8-5D83-42C5-9A8E-C3552ED99DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7B379C-1843-4974-BA31-26A7112A5FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3161B19-ADFC-4891-8B87-EA4EDF3B70A1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3161B19-ADFC-4891-8B87-EA4EDF3B70A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="16">
   <si>
     <t>Asset</t>
   </si>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62F48B75-1141-40F1-8DC4-9CD92F26B175}">
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -505,9 +505,6 @@
       <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
@@ -529,11 +526,7 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <f>B2/C2</f>
-        <v>1.875</v>
-      </c>
-      <c r="F2">
-        <f>E2</f>
+        <f t="shared" ref="E2:E10" si="0">B2/C2</f>
         <v>1.875</v>
       </c>
     </row>
@@ -551,11 +544,7 @@
         <v>6</v>
       </c>
       <c r="E3">
-        <f>B3/C3</f>
-        <v>1.8125</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F5" si="0">E3</f>
+        <f t="shared" si="0"/>
         <v>1.8125</v>
       </c>
       <c r="K3" t="s">
@@ -585,10 +574,6 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <f>B4/C4</f>
-        <v>1.8</v>
-      </c>
-      <c r="F4">
         <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
@@ -619,10 +604,6 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <f>B5/C5</f>
-        <v>2.1666666666666665</v>
-      </c>
-      <c r="F5">
         <f t="shared" si="0"/>
         <v>2.1666666666666665</v>
       </c>
@@ -653,12 +634,8 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <f>B6/C6</f>
+        <f t="shared" si="0"/>
         <v>1.75</v>
-      </c>
-      <c r="F6">
-        <f>(E6*L3)/R3</f>
-        <v>4.375</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -675,12 +652,8 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <f>B7/C7</f>
+        <f t="shared" si="0"/>
         <v>2.1111111111111112</v>
-      </c>
-      <c r="F7">
-        <f>(E7*$L$4)/$R$4</f>
-        <v>0.87962962962962965</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -697,12 +670,8 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <f>B8/C8</f>
+        <f t="shared" si="0"/>
         <v>2</v>
-      </c>
-      <c r="F8">
-        <f>(E8*$L$4)/$R$4</f>
-        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -719,12 +688,8 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <f>B9/C9</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223</v>
-      </c>
-      <c r="F9">
-        <f>(E9*$L$4)/$R$4</f>
-        <v>0.92592592592592604</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -741,12 +706,8 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <f>B10/C10</f>
+        <f t="shared" si="0"/>
         <v>1.7333333333333334</v>
-      </c>
-      <c r="F10">
-        <f>(E10*L5)/R5</f>
-        <v>2.1666666666666665</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -764,10 +725,6 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="F12">
-        <f>AVERAGE(F6:F10)</f>
-        <v>1.836111111111111</v>
-      </c>
       <c r="K12" t="s">
         <v>6</v>
       </c>
@@ -847,20 +804,11 @@
       <c r="L16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="11:19" x14ac:dyDescent="0.25">
       <c r="L17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18">
-        <v>1.75</v>
-      </c>
+    <row r="18" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K18" t="s">
         <v>14</v>
       </c>
@@ -882,45 +830,6 @@
       <c r="S18" s="3">
         <f>AVERAGE(S12:S14)</f>
         <v>2.4737654320987654</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E24">
-        <f>AVERAGE(E18:E21)</f>
-        <v>1.835</v>
       </c>
     </row>
   </sheetData>
